--- a/tools/SHIKA_COLLECTION_カード管理.xlsx
+++ b/tools/SHIKA_COLLECTION_カード管理.xlsx
@@ -2833,6 +2833,11 @@
           <t xml:space="preserve">祭りと文化</t>
         </is>
       </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">051.jpg</t>
+        </is>
+      </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">女性も勇ましくキリコを担ぐことで知られる、全国的にも珍しい祭り。太鼓が響く夕暮れ、日本海を背に神輿とキリコが乱舞し、漁師町ならではの熱気が夜遅くまで続きます。</t>

--- a/tools/SHIKA_COLLECTION_カード管理.xlsx
+++ b/tools/SHIKA_COLLECTION_カード管理.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2ebb8b16c8327f5e/デスクトップ/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_DE7369008EB12A0B818BD21E9D4105A68009FC52" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0BB3D6BB-9140-41DA-BD09-D6EE383BDBA4}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="11_DE7369008EB12A0B818BD21E9D4105A68009FC52" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E6D922A-793A-4437-8F99-ECC07AAAE362}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="11370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="カード管理" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="341">
   <si>
     <t>カードID</t>
   </si>
@@ -593,9 +593,6 @@
     <t>029.jpeg</t>
   </si>
   <si>
-    <t>「あいまぜ」は、主に能登地域で食べられている伝統料理。大根や人参といった根菜類を中心に使った煮物である。使う野菜はその土地土地でとれる旬の野菜が使われるため、見た目や味わいはさまざま。幅広いアレンジがほどこされ、いまに伝わっている。地域性があらわれるのも、この料理の特徴の一つである。 出典：農林水産省「うちの郷土料理」</t>
-  </si>
-  <si>
     <t>030</t>
   </si>
   <si>
@@ -617,9 +614,6 @@
     <t>031.png</t>
   </si>
   <si>
-    <t>志賀町の郷土料理。酒粕に大根や蕪の根菜・葉、こんか漬けのイワシやサバを丸ごと入れて煮込む、ご飯や酒が進む味として親しまれてきた冬の保存食です。</t>
-  </si>
-  <si>
     <t>032</t>
   </si>
   <si>
@@ -677,9 +671,6 @@
     <t>035.jpeg</t>
   </si>
   <si>
-    <t>「日本の白砂青松１００選」にも選ばれる、全長４ｋｍの静かで美しい海岸で、幸せを呼ぶといわれる「さくら貝」が採れます。特に１１月から３月にかけて冬の時期が貝集めのベストシーズンで、さくら貝のほか「三十六歌仙貝」と呼ばれる様々な貝殻が浜辺に打ち寄せられます。</t>
-  </si>
-  <si>
     <t>37.150038,136.707409</t>
   </si>
   <si>
@@ -692,9 +683,6 @@
     <t>036.jpeg</t>
   </si>
   <si>
-    <t>「世界一長いベンチ」に隣接し、増穂浦（ますほがうら）海岸のすぐそばに位置する、海とグルメを楽しめる観光拠点。季節の魚介や農産物、地元ならではの品々がずらり！ぜひ立ち寄りたいスポットです。</t>
-  </si>
-  <si>
     <t>37.140173,136.725168</t>
   </si>
   <si>
@@ -707,9 +695,6 @@
     <t>037.jpeg</t>
   </si>
   <si>
-    <t>１９８９年に「世界一長いベンチ」としてギネスブックに掲載された全長４６０．９ｍのベンチです。日本海に沈む夕日をゆったり眺められ、夏から秋にかけて設置されるイルミネーションは幻想的な雰囲気が楽しめます。</t>
-  </si>
-  <si>
     <t>37.139615,136.724362</t>
   </si>
   <si>
@@ -722,9 +707,6 @@
     <t>038.jpeg</t>
   </si>
   <si>
-    <t>高さ１６ｍと１２ｍの２つの岩が寄り添って並び、しめ縄で結ばれた夫婦岩。志賀町屈指の夕日スポットで夏季、冬季にライトアップされる姿は幻想的です。</t>
-  </si>
-  <si>
     <t>37.122186,136.726767</t>
   </si>
   <si>
@@ -767,9 +749,6 @@
     <t>041.jpeg</t>
   </si>
   <si>
-    <t>荒波で作られた天然の洞窟「巌門」。能登を代表する絶景スポットのひとつです。遊覧船に乗れば、海上から周辺の奇岩とともに雄大な景色が楽しめます。</t>
-  </si>
-  <si>
     <t>37.094349,136.726401</t>
   </si>
   <si>
@@ -782,9 +761,6 @@
     <t>042.jpeg</t>
   </si>
   <si>
-    <t>志賀町福浦港は、古くは渤海国との交流の地として、そして「動く総合商社」とも呼ばれた北前船の寄港地として栄えました。「荒波を越えた男たちの夢が紡いだ異空間～北前船寄港地・船主集落～」の一つとして日本遺産に設定されており、まち歩きすればレトロな風景があちこちに！</t>
-  </si>
-  <si>
     <t>37.083221,136.726773</t>
   </si>
   <si>
@@ -797,9 +773,6 @@
     <t>043.jpeg</t>
   </si>
   <si>
-    <t>当初の建設場所に留まって現在する木造洋式灯台としては、わが国では最古！慶長１３年（１６０８）に、日和山の岸壁上に篝火を焚き、暗夜の海を航行する船を護ったことが最初と伝わります。現存する灯台は明治９年（１８７６）に１７代長兵衛によって建造されました。</t>
-  </si>
-  <si>
     <t>37.083165,136.72313</t>
   </si>
   <si>
@@ -812,9 +785,6 @@
     <t>044.png</t>
   </si>
   <si>
-    <t>「みちのえき旬菜館」では、町の特産品や近隣農家直送の農産物がお手頃な価格で購入できます。温泉施設「アクアパーク　シ・オン」や電源が使えるＲＶパーク※も併設！　※ＲＶパーク・・・安心して車中泊ができる場所</t>
-  </si>
-  <si>
     <t>37.006877,136.780114</t>
   </si>
   <si>
@@ -827,9 +797,6 @@
     <t>045.jpeg</t>
   </si>
   <si>
-    <t>江戸時代には大庄屋として13もの村々を治めた平家。６，０００坪にも及ぶ広大な屋敷地の前庭は、県の名勝に指定されています。歴史を伝える数々の展示も必見！</t>
-  </si>
-  <si>
     <t>37.007666,136.759428</t>
   </si>
   <si>
@@ -893,9 +860,6 @@
     <t>049.jpeg</t>
   </si>
   <si>
-    <t>小貝名所の一つの増穂浦では、１１月から３月にかけて日本海から吹く偏西風「貝よせの風」により、波打ちぎわに小さなさくら貝が打ち寄せられます。気候条件が揃ってこそ現れるさくら貝は「西能登の冬の風物詩」とされ、地元では貝細工にされるなど、「幸せを呼ぶ」貝として親しまれています。</t>
-  </si>
-  <si>
     <t>050</t>
   </si>
   <si>
@@ -905,18 +869,12 @@
     <t>050.jpeg</t>
   </si>
   <si>
-    <t>約３０基のキリコが太鼓や鐘の音に合わせて街を練り歩き、参道から境内へ駆け上がる様子は圧巻！男神と女神の年に一度の逢瀬から始まったと言われます。</t>
-  </si>
-  <si>
     <t>051</t>
   </si>
   <si>
     <t>西海祭り</t>
   </si>
   <si>
-    <t>女性も勇ましくキリコを担ぐことで知られる、全国的にも珍しい祭り。太鼓が響く夕暮れ、日本海を背に神輿とキリコが乱舞し、漁師町ならではの熱気が夜遅くまで続きます。</t>
-  </si>
-  <si>
     <t>052</t>
   </si>
   <si>
@@ -926,9 +884,6 @@
     <t>052.jpeg</t>
   </si>
   <si>
-    <t>福浦港の総鎮守社である猿田彦神社の秋季祭礼。猿田彦神社から海上渡御を行う神様船までの間を天狗が先導し、町民が仮装行列して盛り上げます。志賀町の指定無形民俗文化財。</t>
-  </si>
-  <si>
     <t>053</t>
   </si>
   <si>
@@ -938,9 +893,6 @@
     <t>053.jpeg</t>
   </si>
   <si>
-    <t>石川県志賀町の獅子舞は、秋祭りに奉納される伝統芸能。巨大な蚊帳獅子と天狗（獅子捕り）が対峙する躍動感あふれる演舞が特徴で、無病息災や五穀豊穣を祈願します。</t>
-  </si>
-  <si>
     <t>SHIKA COLLECTION｜カード管理</t>
   </si>
   <si>
@@ -1032,13 +984,6 @@
   </si>
   <si>
     <t>この表には写真を貼らないでください。ファイルが巨大になり、扱えなくなります。</t>
-  </si>
-  <si>
-    <t>木の型を使い、酢飯に紅鮭を挟んだ押しずし。かつては、船乗りが保存食として蓄えた塩漬けの紅鮭を使って作られていました。祭りや正月、家の建前などの祝い事に振る舞われています。</t>
-    <rPh sb="7" eb="9">
-      <t>スメシ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>冨木八朔祭礼</t>
@@ -1049,6 +994,90 @@
   </si>
   <si>
     <t>051.jpeg</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>能登地域で食べられている伝統料理。大根や人参といった根菜類を中心に使った煮物です。</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>志賀町の郷土料理。酒粕に大根や蕪の根菜・葉、こんか漬けのイワシやサバを丸ごと入れて煮込む冬の保存食です。</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>木の型を使い、酢飯に紅鮭を挟んだ押しずし。祭りや正月、家の建前などの祝い事に振る舞われています。</t>
+    <rPh sb="7" eb="9">
+      <t>スメシ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>「日本の白砂青松１００選」にも選ばれる、全長４ｋｍの静かで美しい海岸で、幸せを呼ぶといわれる「さくら貝」が採れます。</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>「世界一長いベンチ」に隣接し、増穂浦（ますほがうら）海岸のすぐそばに位置する、海とグルメを楽しめる観光拠点。</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>１９８９年に「世界一長いベンチ」としてギネスブックに掲載された全長４６０．９ｍのベンチです。</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>「荒波を越えた男たちの夢が紡いだ異空間～北前船寄港地・船主集落～」の一つとして日本遺産に設定されています。</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>当初の建設場所に留まって現存する木造洋式灯台としては、日本最古！明治９年（１８７６）に建造されました。</t>
+    <rPh sb="13" eb="14">
+      <t>ゾン</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ニホン</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>町の特産品や近隣農家直送の農産物がお手頃な価格で購入できます。温泉施設「アクアパーク　シ・オン」も併設しています。</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>江戸時代には大庄屋として13もの村々を治めた平家。６，０００坪にも及ぶ広大な屋敷地の前庭は、県の名勝に指定されています。</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>偏西風により打ち寄せられる、さくら貝は「西能登の冬の風物詩」とされ、「幸せを呼ぶ」貝として親しまれています。</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>約３０基のキリコが太鼓や鐘の音に合わせて街を練り歩き、参道から境内へ駆け上がる様子は圧巻！</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>女性も勇ましくキリコを担ぐことで知られる、全国的にも珍しい祭り。漁師町ならではの熱気が夜遅くまで続きます。</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>高さ１６ｍと１２ｍの２つの岩が寄り添って並び、しめ縄で結ばれた夫婦岩。志賀町屈指の夕日スポットです。</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>荒波で作られた天然の洞窟「巌門」。能登を代表する絶景スポットのひとつです。遊覧船からの雄大な景色もお勧め。</t>
+    <rPh sb="50" eb="51">
+      <t>スス</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>巨大な蚊帳獅子と天狗（獅子捕り）が対峙する躍動感あふれる演舞が特徴で、無病息災や五穀豊穣を祈願します。</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>海上渡御を行う神様船までの間を天狗が先導し、町民が仮装行列して盛り上げます。志賀町の指定無形民俗文化財。</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>コクのある濃厚な旨味とまろやかな口当たりが特徴で、ひと口食べれば磯の香りと芳醇なコクが口いっぱいに広がります。</t>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -1132,6 +1161,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1828,6 +1861,9 @@
       <c r="F9" s="2" t="s">
         <v>73</v>
       </c>
+      <c r="I9" s="2" t="s">
+        <v>340</v>
+      </c>
       <c r="J9" s="2" t="s">
         <v>59</v>
       </c>
@@ -2499,7 +2535,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="108" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="2" t="s">
         <v>186</v>
       </c>
@@ -2519,15 +2555,15 @@
         <v>189</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>190</v>
+        <v>323</v>
       </c>
     </row>
     <row r="31" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B31" s="2" t="s">
         <v>191</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>192</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>30</v>
@@ -2539,18 +2575,18 @@
         <v>188</v>
       </c>
       <c r="F31" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="I31" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="I31" s="2" t="s">
+    </row>
+    <row r="32" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" s="2" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="32" spans="1:17" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="2" t="s">
+      <c r="B32" s="2" t="s">
         <v>195</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>196</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>30</v>
@@ -2562,21 +2598,21 @@
         <v>188</v>
       </c>
       <c r="F32" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="O32" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="I32" s="2" t="s">
+      <c r="B33" s="2" t="s">
         <v>198</v>
-      </c>
-      <c r="O32" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>200</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>30</v>
@@ -2588,235 +2624,235 @@
         <v>188</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="O33" s="2" t="s">
         <v>31</v>
       </c>
       <c r="P33" s="2"/>
       <c r="Q33" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="34" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="D34" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="F34" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="I34" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="D34" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="F34" s="2" t="s">
+      <c r="L34" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="I34" s="2" t="s">
+      <c r="M34" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="N34" s="2" t="s">
         <v>207</v>
-      </c>
-      <c r="L34" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="M34" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="N34" s="2" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="35" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="F35" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="I35" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="C35" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="F35" s="2" t="s">
+      <c r="L35" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="I35" s="2" t="s">
+      <c r="M35" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="N35" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="L35" s="2" t="s">
+      <c r="B36" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="M35" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="N35" s="2" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" ht="90" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="2" t="s">
+      <c r="C36" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="F36" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="I36" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="L36" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="C36" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="F36" s="2" t="s">
+      <c r="M36" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="N36" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="I36" s="2" t="s">
+      <c r="B37" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="L36" s="2" t="s">
+      <c r="C37" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="F37" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="M36" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="N36" s="2" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="2" t="s">
+      <c r="I37" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="L37" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="M37" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="N37" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="C37" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="F37" s="2" t="s">
+      <c r="B38" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="I37" s="2" t="s">
+      <c r="C38" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="F38" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="L37" s="2" t="s">
+      <c r="I38" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="L38" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="M37" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="N37" s="2" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17" ht="72" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="2" t="s">
+      <c r="M38" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="N38" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="B39" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="C38" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="F38" s="2" t="s">
+      <c r="C39" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="F39" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="I38" s="2" t="s">
+      <c r="I39" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="L39" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="M38" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="N38" s="2" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="39" spans="1:17" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="I39" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="L39" s="2" t="s">
-        <v>234</v>
-      </c>
       <c r="M39" s="2" t="s">
         <v>31</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="40" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="2" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="M40" s="2" t="s">
         <v>31</v>
@@ -2827,28 +2863,28 @@
     </row>
     <row r="41" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="2" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="M41" s="2" t="s">
         <v>31</v>
@@ -2857,378 +2893,378 @@
         <v>200</v>
       </c>
     </row>
-    <row r="42" spans="1:17" ht="54" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="L42" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="M42" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="N42" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="F43" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="I43" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="L43" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="C42" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="F42" s="2" t="s">
+      <c r="M43" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="N43" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="I42" s="2" t="s">
+      <c r="B44" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="L42" s="2" t="s">
+      <c r="C44" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="F44" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="M42" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="N42" s="2" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="43" spans="1:17" ht="90" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43" s="2" t="s">
+      <c r="I44" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="L44" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="M44" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="N44" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="C43" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="F43" s="2" t="s">
+      <c r="B45" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="I43" s="2" t="s">
+      <c r="C45" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="F45" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="L43" s="2" t="s">
+      <c r="I45" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="L45" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="M43" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="N43" s="2" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="44" spans="1:17" ht="72" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" s="2" t="s">
+      <c r="M45" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="N45" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A46" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="B46" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="C44" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="F44" s="2" t="s">
+      <c r="C46" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="F46" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="I44" s="2" t="s">
+      <c r="I46" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="L46" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="L44" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="M44" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="N44" s="2" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="45" spans="1:17" ht="72" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="I45" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="L45" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="M45" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="N45" s="2" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="46" spans="1:17" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="I46" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="L46" s="2" t="s">
-        <v>269</v>
-      </c>
       <c r="M46" s="2" t="s">
         <v>31</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="47" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="2" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>271</v>
+        <v>260</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>272</v>
+        <v>261</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>273</v>
+        <v>262</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="M47" s="2" t="s">
         <v>31</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="48" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="2" t="s">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="M48" s="2" t="s">
         <v>31</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="49" spans="1:14" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="2" t="s">
-        <v>280</v>
+        <v>269</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="M49" s="2" t="s">
         <v>31</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="50" spans="1:14" ht="90" x14ac:dyDescent="0.55000000000000004">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="2" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>287</v>
+        <v>276</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>288</v>
+        <v>277</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>290</v>
+        <v>333</v>
       </c>
       <c r="J50" s="2" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="51" spans="1:14" ht="54" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:14" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" s="2" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="B51" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="I51" s="2" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A52" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A53" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="I53" s="2" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A54" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="I54" s="2" t="s">
         <v>338</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="I51" s="2" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="52" spans="1:14" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="A52" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="F52" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="I52" s="2" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="53" spans="1:14" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="A53" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="F53" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="I53" s="2" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="54" spans="1:14" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="A54" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="F54" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="I54" s="2" t="s">
-        <v>305</v>
       </c>
     </row>
   </sheetData>
@@ -3248,63 +3284,63 @@
   <sheetData>
     <row r="1" spans="1:2" ht="22.5" x14ac:dyDescent="0.65">
       <c r="A1" s="3" t="s">
-        <v>306</v>
+        <v>290</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
-        <v>307</v>
+        <v>291</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>308</v>
+        <v>292</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
-        <v>309</v>
+        <v>293</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>310</v>
+        <v>294</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
-        <v>311</v>
+        <v>295</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>312</v>
+        <v>296</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
-        <v>313</v>
+        <v>297</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>314</v>
+        <v>298</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
-        <v>315</v>
+        <v>299</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>316</v>
+        <v>300</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="1" t="s">
-        <v>317</v>
+        <v>301</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>318</v>
+        <v>302</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="1" t="s">
-        <v>319</v>
+        <v>303</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3312,15 +3348,15 @@
         <v>0</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>321</v>
+        <v>305</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="1" t="s">
-        <v>322</v>
+        <v>306</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>323</v>
+        <v>307</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3328,7 +3364,7 @@
         <v>2</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>324</v>
+        <v>308</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3336,7 +3372,7 @@
         <v>3</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>325</v>
+        <v>309</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3344,7 +3380,7 @@
         <v>5</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>326</v>
+        <v>310</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3352,7 +3388,7 @@
         <v>6</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>327</v>
+        <v>311</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3360,7 +3396,7 @@
         <v>8</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>328</v>
+        <v>312</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3368,7 +3404,7 @@
         <v>7</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>329</v>
+        <v>313</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3376,7 +3412,7 @@
         <v>11</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>330</v>
+        <v>314</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3384,7 +3420,7 @@
         <v>12</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>331</v>
+        <v>315</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3392,23 +3428,23 @@
         <v>15</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>332</v>
+        <v>316</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="1" t="s">
-        <v>333</v>
+        <v>317</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>334</v>
+        <v>318</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="1" t="s">
-        <v>335</v>
+        <v>319</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>336</v>
+        <v>320</v>
       </c>
     </row>
   </sheetData>

--- a/tools/SHIKA_COLLECTION_カード管理.xlsx
+++ b/tools/SHIKA_COLLECTION_カード管理.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2ebb8b16c8327f5e/デスクトップ/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="11_DE7369008EB12A0B818BD21E9D4105A68009FC52" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E6D922A-793A-4437-8F99-ECC07AAAE362}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="11_DE7369008EB12A0B818BD21E9D4105A68009FC52" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2FD49CA0-CEC4-4B18-86B2-C750735179B2}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -671,9 +671,6 @@
     <t>035.jpeg</t>
   </si>
   <si>
-    <t>37.150038,136.707409</t>
-  </si>
-  <si>
     <t>036</t>
   </si>
   <si>
@@ -735,9 +732,6 @@
   </si>
   <si>
     <t>山容の美しさから「能登富士」と呼ばれ、神体山としても仰がれています。</t>
-  </si>
-  <si>
-    <t>37.206952,136.724368</t>
   </si>
   <si>
     <t>041</t>
@@ -1079,6 +1073,12 @@
   <si>
     <t>コクのある濃厚な旨味とまろやかな口当たりが特徴で、ひと口食べれば磯の香りと芳醇なコクが口いっぱいに広がります。</t>
     <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>37.13942168208599, 136.72402758326442</t>
+  </si>
+  <si>
+    <t>37.19203617709108, 136.717235868344</t>
   </si>
 </sst>
 </file>
@@ -1862,7 +1862,7 @@
         <v>73</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>59</v>
@@ -2555,7 +2555,7 @@
         <v>189</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="31" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
@@ -2601,7 +2601,7 @@
         <v>196</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="O32" s="2" t="s">
         <v>31</v>
@@ -2627,7 +2627,7 @@
         <v>199</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="O33" s="2" t="s">
         <v>31</v>
@@ -2721,10 +2721,10 @@
         <v>215</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>216</v>
+        <v>339</v>
       </c>
       <c r="M36" s="2" t="s">
         <v>31</v>
@@ -2735,10 +2735,10 @@
     </row>
     <row r="37" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B37" s="2" t="s">
         <v>217</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>218</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>203</v>
@@ -2750,13 +2750,13 @@
         <v>203</v>
       </c>
       <c r="F37" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="L37" s="2" t="s">
         <v>219</v>
-      </c>
-      <c r="I37" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="L37" s="2" t="s">
-        <v>220</v>
       </c>
       <c r="M37" s="2" t="s">
         <v>31</v>
@@ -2767,10 +2767,10 @@
     </row>
     <row r="38" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="B38" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>222</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>203</v>
@@ -2782,13 +2782,13 @@
         <v>203</v>
       </c>
       <c r="F38" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="L38" s="2" t="s">
         <v>223</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="L38" s="2" t="s">
-        <v>224</v>
       </c>
       <c r="M38" s="2" t="s">
         <v>31</v>
@@ -2799,10 +2799,10 @@
     </row>
     <row r="39" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B39" s="2" t="s">
         <v>225</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>226</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>203</v>
@@ -2814,13 +2814,13 @@
         <v>203</v>
       </c>
       <c r="F39" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="I39" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="L39" s="2" t="s">
         <v>227</v>
-      </c>
-      <c r="I39" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="L39" s="2" t="s">
-        <v>228</v>
       </c>
       <c r="M39" s="2" t="s">
         <v>31</v>
@@ -2831,10 +2831,10 @@
     </row>
     <row r="40" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="B40" s="2" t="s">
         <v>229</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>230</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>203</v>
@@ -2846,13 +2846,13 @@
         <v>203</v>
       </c>
       <c r="F40" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="I40" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="I40" s="2" t="s">
+      <c r="L40" s="2" t="s">
         <v>232</v>
-      </c>
-      <c r="L40" s="2" t="s">
-        <v>233</v>
       </c>
       <c r="M40" s="2" t="s">
         <v>31</v>
@@ -2863,10 +2863,10 @@
     </row>
     <row r="41" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="B41" s="2" t="s">
         <v>234</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>235</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>203</v>
@@ -2878,13 +2878,13 @@
         <v>203</v>
       </c>
       <c r="F41" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="I41" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="I41" s="2" t="s">
-        <v>237</v>
-      </c>
       <c r="L41" s="2" t="s">
-        <v>238</v>
+        <v>340</v>
       </c>
       <c r="M41" s="2" t="s">
         <v>31</v>
@@ -2895,10 +2895,10 @@
     </row>
     <row r="42" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>203</v>
@@ -2910,13 +2910,13 @@
         <v>203</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="M42" s="2" t="s">
         <v>31</v>
@@ -2927,10 +2927,10 @@
     </row>
     <row r="43" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>203</v>
@@ -2942,13 +2942,13 @@
         <v>203</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="M43" s="2" t="s">
         <v>31</v>
@@ -2959,10 +2959,10 @@
     </row>
     <row r="44" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>203</v>
@@ -2974,13 +2974,13 @@
         <v>203</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="M44" s="2" t="s">
         <v>31</v>
@@ -2991,10 +2991,10 @@
     </row>
     <row r="45" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>203</v>
@@ -3006,13 +3006,13 @@
         <v>203</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="M45" s="2" t="s">
         <v>31</v>
@@ -3023,10 +3023,10 @@
     </row>
     <row r="46" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>203</v>
@@ -3038,13 +3038,13 @@
         <v>203</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="M46" s="2" t="s">
         <v>31</v>
@@ -3055,10 +3055,10 @@
     </row>
     <row r="47" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>203</v>
@@ -3070,13 +3070,13 @@
         <v>203</v>
       </c>
       <c r="F47" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="L47" s="2" t="s">
         <v>261</v>
-      </c>
-      <c r="I47" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="L47" s="2" t="s">
-        <v>263</v>
       </c>
       <c r="M47" s="2" t="s">
         <v>31</v>
@@ -3087,10 +3087,10 @@
     </row>
     <row r="48" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>203</v>
@@ -3102,13 +3102,13 @@
         <v>203</v>
       </c>
       <c r="F48" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="L48" s="2" t="s">
         <v>266</v>
-      </c>
-      <c r="I48" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="L48" s="2" t="s">
-        <v>268</v>
       </c>
       <c r="M48" s="2" t="s">
         <v>31</v>
@@ -3119,10 +3119,10 @@
     </row>
     <row r="49" spans="1:14" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>203</v>
@@ -3134,13 +3134,13 @@
         <v>203</v>
       </c>
       <c r="F49" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="I49" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="L49" s="2" t="s">
         <v>271</v>
-      </c>
-      <c r="I49" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="L49" s="2" t="s">
-        <v>273</v>
       </c>
       <c r="M49" s="2" t="s">
         <v>31</v>
@@ -3151,25 +3151,25 @@
     </row>
     <row r="50" spans="1:14" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="C50" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="D50" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E50" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="F50" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D50" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="F50" s="2" t="s">
-        <v>278</v>
-      </c>
       <c r="I50" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="J50" s="2" t="s">
         <v>59</v>
@@ -3177,94 +3177,94 @@
     </row>
     <row r="51" spans="1:14" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="F51" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>281</v>
-      </c>
       <c r="I51" s="2" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="52" spans="1:14" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="53" spans="1:14" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="F53" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="B53" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="F53" s="2" t="s">
-        <v>286</v>
-      </c>
       <c r="I53" s="2" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="54" spans="1:14" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="F54" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="B54" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="F54" s="2" t="s">
-        <v>289</v>
-      </c>
       <c r="I54" s="2" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
   </sheetData>
@@ -3284,63 +3284,63 @@
   <sheetData>
     <row r="1" spans="1:2" ht="22.5" x14ac:dyDescent="0.65">
       <c r="A1" s="3" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="1" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3348,15 +3348,15 @@
         <v>0</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3364,7 +3364,7 @@
         <v>2</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3372,7 +3372,7 @@
         <v>3</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3380,7 +3380,7 @@
         <v>5</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3388,7 +3388,7 @@
         <v>6</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3396,7 +3396,7 @@
         <v>8</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3404,7 +3404,7 @@
         <v>7</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3412,7 +3412,7 @@
         <v>11</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3420,7 +3420,7 @@
         <v>12</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3428,23 +3428,23 @@
         <v>15</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
   </sheetData>

--- a/tools/SHIKA_COLLECTION_カード管理.xlsx
+++ b/tools/SHIKA_COLLECTION_カード管理.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2ebb8b16c8327f5e/デスクトップ/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="11_DE7369008EB12A0B818BD21E9D4105A68009FC52" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2FD49CA0-CEC4-4B18-86B2-C750735179B2}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="11_DE7369008EB12A0B818BD21E9D4105A68009FC52" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B5C1F418-94F4-4F0D-A375-27B1BCC85EC7}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -302,9 +302,6 @@
     <t>012</t>
   </si>
   <si>
-    <t>能登牛（のとうし）</t>
-  </si>
-  <si>
     <t>山の幸</t>
   </si>
   <si>
@@ -596,9 +593,6 @@
     <t>030</t>
   </si>
   <si>
-    <t>お汁（お祭り）</t>
-  </si>
-  <si>
     <t>030.jpeg</t>
   </si>
   <si>
@@ -749,9 +743,6 @@
     <t>042</t>
   </si>
   <si>
-    <t>日本遺産　北前船寄港地福浦港</t>
-  </si>
-  <si>
     <t>042.jpeg</t>
   </si>
   <si>
@@ -773,9 +764,6 @@
     <t>044</t>
   </si>
   <si>
-    <t>道の駅　ころ柿の里しか（みちのえき旬菜館）</t>
-  </si>
-  <si>
     <t>044.png</t>
   </si>
   <si>
@@ -825,9 +813,6 @@
   </si>
   <si>
     <t>048</t>
-  </si>
-  <si>
-    <t>大島キャンプ場（海水浴場）</t>
   </si>
   <si>
     <t>048.jpeg</t>
@@ -1079,6 +1064,26 @@
   </si>
   <si>
     <t>37.19203617709108, 136.717235868344</t>
+  </si>
+  <si>
+    <t>福浦港</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>道の駅　ころ柿の里しか</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>大島キャンプ場</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>お汁</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>能登牛（のとうし）</t>
+    <phoneticPr fontId="3"/>
   </si>
 </sst>
 </file>
@@ -1862,7 +1867,7 @@
         <v>73</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>59</v>
@@ -1987,7 +1992,7 @@
         <v>92</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>93</v>
+        <v>340</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>30</v>
@@ -1996,13 +2001,13 @@
         <v>31</v>
       </c>
       <c r="E13" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="I13" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>96</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>59</v>
@@ -2014,15 +2019,15 @@
         <v>31</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:28" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>98</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>99</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>30</v>
@@ -2031,13 +2036,13 @@
         <v>31</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F14" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>100</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>101</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>59</v>
@@ -2049,15 +2054,15 @@
         <v>31</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15" spans="1:28" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>103</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>104</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>30</v>
@@ -2066,33 +2071,33 @@
         <v>31</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F15" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="I15" s="2" t="s">
+      <c r="J15" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="J15" s="2" t="s">
+      <c r="O15" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q15" s="2" t="s">
         <v>107</v>
-      </c>
-      <c r="O15" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="P15" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q15" s="2" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="16" spans="1:28" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>109</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>110</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>30</v>
@@ -2101,30 +2106,30 @@
         <v>31</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F16" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="I16" s="2" t="s">
+      <c r="J16" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="J16" s="2" t="s">
+      <c r="P16" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q16" s="2" t="s">
         <v>113</v>
-      </c>
-      <c r="P16" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q16" s="2" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="17" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>116</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>30</v>
@@ -2133,30 +2138,30 @@
         <v>31</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F17" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="I17" s="2" t="s">
+      <c r="J17" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="J17" s="2" t="s">
+      <c r="P17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q17" s="2" t="s">
         <v>119</v>
-      </c>
-      <c r="P17" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q17" s="2" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="18" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>121</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>122</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>30</v>
@@ -2165,30 +2170,30 @@
         <v>31</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F18" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="I18" s="2" t="s">
+      <c r="J18" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="J18" s="2" t="s">
+      <c r="P18" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q18" s="2" t="s">
         <v>125</v>
-      </c>
-      <c r="P18" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q18" s="2" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="19" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>127</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>128</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>30</v>
@@ -2197,30 +2202,30 @@
         <v>31</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F19" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="I19" s="2" t="s">
+      <c r="J19" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="J19" s="2" t="s">
+      <c r="P19" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q19" s="2" t="s">
         <v>131</v>
-      </c>
-      <c r="P19" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q19" s="2" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="20" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>133</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>134</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>30</v>
@@ -2229,30 +2234,30 @@
         <v>31</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F20" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="I20" s="2" t="s">
+      <c r="J20" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q20" s="2" t="s">
         <v>136</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="P20" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q20" s="2" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="21" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>138</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>139</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>30</v>
@@ -2261,30 +2266,30 @@
         <v>31</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F21" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="I21" s="2" t="s">
+      <c r="J21" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="J21" s="2" t="s">
+      <c r="P21" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q21" s="2" t="s">
         <v>142</v>
-      </c>
-      <c r="P21" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q21" s="2" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="22" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>144</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>145</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>30</v>
@@ -2293,13 +2298,13 @@
         <v>31</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F22" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="I22" s="2" t="s">
         <v>146</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>147</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>59</v>
@@ -2308,15 +2313,15 @@
         <v>31</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="23" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>149</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>150</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>30</v>
@@ -2325,13 +2330,13 @@
         <v>31</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F23" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>151</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>152</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>59</v>
@@ -2340,15 +2345,15 @@
         <v>31</v>
       </c>
       <c r="Q23" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="24" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>154</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>155</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>30</v>
@@ -2357,30 +2362,30 @@
         <v>31</v>
       </c>
       <c r="E24" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="F24" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="F24" s="2" t="s">
+      <c r="I24" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="I24" s="2" t="s">
+      <c r="J24" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="J24" s="2" t="s">
+      <c r="P24" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q24" s="2" t="s">
         <v>159</v>
-      </c>
-      <c r="P24" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q24" s="2" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="25" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>161</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>162</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>30</v>
@@ -2389,13 +2394,13 @@
         <v>31</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F25" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>163</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>164</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>53</v>
@@ -2404,15 +2409,15 @@
         <v>31</v>
       </c>
       <c r="Q25" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="26" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>30</v>
@@ -2421,13 +2426,13 @@
         <v>31</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F26" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="I26" s="2" t="s">
         <v>168</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>169</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>53</v>
@@ -2436,15 +2441,15 @@
         <v>31</v>
       </c>
       <c r="Q26" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="27" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>171</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>172</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>30</v>
@@ -2453,13 +2458,13 @@
         <v>31</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F27" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="I27" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>174</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>59</v>
@@ -2468,15 +2473,15 @@
         <v>31</v>
       </c>
       <c r="Q27" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="28" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>176</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>177</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>30</v>
@@ -2485,13 +2490,13 @@
         <v>31</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F28" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>179</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>59</v>
@@ -2500,15 +2505,15 @@
         <v>31</v>
       </c>
       <c r="Q28" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="29" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B29" s="2" t="s">
         <v>181</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>182</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>30</v>
@@ -2517,13 +2522,13 @@
         <v>31</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F29" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="I29" s="2" t="s">
         <v>183</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>184</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>59</v>
@@ -2532,15 +2537,15 @@
         <v>31</v>
       </c>
       <c r="Q29" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="30" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B30" s="2" t="s">
         <v>186</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>187</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>30</v>
@@ -2549,21 +2554,21 @@
         <v>31</v>
       </c>
       <c r="E30" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="F30" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="F30" s="2" t="s">
-        <v>189</v>
-      </c>
       <c r="I30" s="2" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
     </row>
     <row r="31" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>191</v>
+        <v>339</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>30</v>
@@ -2572,21 +2577,21 @@
         <v>31</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="32" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>30</v>
@@ -2595,13 +2600,13 @@
         <v>31</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="O32" s="2" t="s">
         <v>31</v>
@@ -2609,10 +2614,10 @@
     </row>
     <row r="33" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>30</v>
@@ -2621,238 +2626,238 @@
         <v>31</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="O33" s="2" t="s">
         <v>31</v>
       </c>
       <c r="P33" s="2"/>
       <c r="Q33" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="34" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="D34" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="F34" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="I34" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="D34" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="F34" s="2" t="s">
+      <c r="L34" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="I34" s="2" t="s">
+      <c r="M34" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="N34" s="2" t="s">
         <v>205</v>
-      </c>
-      <c r="L34" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="M34" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="N34" s="2" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="35" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="F35" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="I35" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="C35" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="F35" s="2" t="s">
+      <c r="L35" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="I35" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="L35" s="2" t="s">
-        <v>212</v>
-      </c>
       <c r="M35" s="2" t="s">
         <v>31</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="36" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="F36" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>215</v>
-      </c>
       <c r="I36" s="2" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="M36" s="2" t="s">
         <v>31</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="37" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="F37" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="I37" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="L37" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="C37" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="I37" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="L37" s="2" t="s">
-        <v>219</v>
-      </c>
       <c r="M37" s="2" t="s">
         <v>31</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="38" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="F38" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="I38" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="L38" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="C38" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="L38" s="2" t="s">
-        <v>223</v>
-      </c>
       <c r="M38" s="2" t="s">
         <v>31</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="39" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="F39" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="I39" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="L39" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="C39" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="I39" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="L39" s="2" t="s">
-        <v>227</v>
-      </c>
       <c r="M39" s="2" t="s">
         <v>31</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="40" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="F40" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="I40" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="C40" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="F40" s="2" t="s">
+      <c r="L40" s="2" t="s">
         <v>230</v>
-      </c>
-      <c r="I40" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="L40" s="2" t="s">
-        <v>232</v>
       </c>
       <c r="M40" s="2" t="s">
         <v>31</v>
@@ -2863,28 +2868,28 @@
     </row>
     <row r="41" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="F41" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="I41" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="C41" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="I41" s="2" t="s">
-        <v>236</v>
-      </c>
       <c r="L41" s="2" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="M41" s="2" t="s">
         <v>31</v>
@@ -2895,281 +2900,281 @@
     </row>
     <row r="42" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="F42" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="I42" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="L42" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="C42" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="I42" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="L42" s="2" t="s">
-        <v>240</v>
-      </c>
       <c r="M42" s="2" t="s">
         <v>31</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="43" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="L43" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="I43" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="L43" s="2" t="s">
-        <v>244</v>
-      </c>
       <c r="M43" s="2" t="s">
         <v>31</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="44" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="L44" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="I44" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="L44" s="2" t="s">
-        <v>248</v>
-      </c>
       <c r="M44" s="2" t="s">
         <v>31</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="45" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="2" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>250</v>
+        <v>337</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="M45" s="2" t="s">
         <v>31</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="46" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="2" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="M46" s="2" t="s">
         <v>31</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="47" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="L47" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B47" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="I47" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="L47" s="2" t="s">
-        <v>261</v>
-      </c>
       <c r="M47" s="2" t="s">
         <v>31</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="48" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="L48" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="B48" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="F48" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="I48" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="L48" s="2" t="s">
-        <v>266</v>
-      </c>
       <c r="M48" s="2" t="s">
         <v>31</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="49" spans="1:14" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="2" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>268</v>
+        <v>338</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="M49" s="2" t="s">
         <v>31</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="50" spans="1:14" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="2" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="J50" s="2" t="s">
         <v>59</v>
@@ -3177,94 +3182,94 @@
     </row>
     <row r="51" spans="1:14" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" s="2" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="C51" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="F51" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="D51" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>279</v>
-      </c>
       <c r="I51" s="2" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
     </row>
     <row r="52" spans="1:14" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" s="2" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
     </row>
     <row r="53" spans="1:14" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" s="2" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
     </row>
     <row r="54" spans="1:14" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="2" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
     </row>
   </sheetData>
@@ -3284,63 +3289,63 @@
   <sheetData>
     <row r="1" spans="1:2" ht="22.5" x14ac:dyDescent="0.65">
       <c r="A1" s="3" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="1" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="1" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3348,15 +3353,15 @@
         <v>0</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="1" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3364,7 +3369,7 @@
         <v>2</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3372,7 +3377,7 @@
         <v>3</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3380,7 +3385,7 @@
         <v>5</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3388,7 +3393,7 @@
         <v>6</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3396,7 +3401,7 @@
         <v>8</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3404,7 +3409,7 @@
         <v>7</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3412,7 +3417,7 @@
         <v>11</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3420,7 +3425,7 @@
         <v>12</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3428,23 +3433,23 @@
         <v>15</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="1" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="1" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
     </row>
   </sheetData>
